--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/DAT/DAT+50T+50EP+optim_purn/params_vs_psnr_analysis/DAT_hutcn_hyperopt_study_3cols.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/DAT/DAT+50T+50EP+optim_purn/params_vs_psnr_analysis/DAT_hutcn_hyperopt_study_3cols.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FLOPs (G) @ 48x48</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>PSNR (dB)</t>
         </is>
       </c>
@@ -453,6 +458,9 @@
         <v>531622</v>
       </c>
       <c r="C2" t="n">
+        <v>1.16176302</v>
+      </c>
+      <c r="D2" t="n">
         <v>27.65851249694824</v>
       </c>
     </row>
@@ -464,6 +472,9 @@
         <v>626264</v>
       </c>
       <c r="C3" t="n">
+        <v>1.277049024</v>
+      </c>
+      <c r="D3" t="n">
         <v>28.04580268859863</v>
       </c>
     </row>
@@ -475,6 +486,9 @@
         <v>531622</v>
       </c>
       <c r="C4" t="n">
+        <v>1.16176302</v>
+      </c>
+      <c r="D4" t="n">
         <v>27.6333381652832</v>
       </c>
     </row>
@@ -486,6 +500,9 @@
         <v>626264</v>
       </c>
       <c r="C5" t="n">
+        <v>1.277049024</v>
+      </c>
+      <c r="D5" t="n">
         <v>28.05669136047363</v>
       </c>
     </row>
@@ -497,6 +514,9 @@
         <v>861360</v>
       </c>
       <c r="C6" t="n">
+        <v>1.999435968</v>
+      </c>
+      <c r="D6" t="n">
         <v>29.12904663085937</v>
       </c>
     </row>
@@ -508,6 +528,9 @@
         <v>293808</v>
       </c>
       <c r="C7" t="n">
+        <v>0.75007872</v>
+      </c>
+      <c r="D7" t="n">
         <v>29.32546653747558</v>
       </c>
     </row>
@@ -519,6 +542,9 @@
         <v>746364</v>
       </c>
       <c r="C8" t="n">
+        <v>1.893046464</v>
+      </c>
+      <c r="D8" t="n">
         <v>30.61105842590332</v>
       </c>
     </row>
@@ -530,6 +556,9 @@
         <v>1141866</v>
       </c>
       <c r="C9" t="n">
+        <v>2.53528542</v>
+      </c>
+      <c r="D9" t="n">
         <v>28.45059852600098</v>
       </c>
     </row>
@@ -541,6 +570,9 @@
         <v>442540</v>
       </c>
       <c r="C10" t="n">
+        <v>0.90653112</v>
+      </c>
+      <c r="D10" t="n">
         <v>27.87301712036133</v>
       </c>
     </row>
@@ -552,6 +584,9 @@
         <v>298040</v>
       </c>
       <c r="C11" t="n">
+        <v>0.75007872</v>
+      </c>
+      <c r="D11" t="n">
         <v>27.85956382751465</v>
       </c>
     </row>
@@ -563,6 +598,9 @@
         <v>1021988</v>
       </c>
       <c r="C12" t="n">
+        <v>2.478846384</v>
+      </c>
+      <c r="D12" t="n">
         <v>30.13947143554687</v>
       </c>
     </row>
@@ -574,6 +612,9 @@
         <v>1021988</v>
       </c>
       <c r="C13" t="n">
+        <v>2.478846384</v>
+      </c>
+      <c r="D13" t="n">
         <v>30.57269096374512</v>
       </c>
     </row>
@@ -585,6 +626,9 @@
         <v>1560312</v>
       </c>
       <c r="C14" t="n">
+        <v>3.77445888</v>
+      </c>
+      <c r="D14" t="n">
         <v>30.87657127380371</v>
       </c>
     </row>
@@ -596,6 +640,9 @@
         <v>1560312</v>
       </c>
       <c r="C15" t="n">
+        <v>3.77445888</v>
+      </c>
+      <c r="D15" t="n">
         <v>30.8380729675293</v>
       </c>
     </row>
@@ -607,6 +654,9 @@
         <v>1560312</v>
       </c>
       <c r="C16" t="n">
+        <v>3.77445888</v>
+      </c>
+      <c r="D16" t="n">
         <v>30.43733215332031</v>
       </c>
     </row>
@@ -618,6 +668,9 @@
         <v>1560312</v>
       </c>
       <c r="C17" t="n">
+        <v>3.77445888</v>
+      </c>
+      <c r="D17" t="n">
         <v>30.17931823730469</v>
       </c>
     </row>
@@ -629,6 +682,9 @@
         <v>1498872</v>
       </c>
       <c r="C18" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D18" t="n">
         <v>30.78531341552734</v>
       </c>
     </row>
@@ -640,6 +696,9 @@
         <v>1498872</v>
       </c>
       <c r="C19" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D19" t="n">
         <v>30.7643627166748</v>
       </c>
     </row>
@@ -651,6 +710,9 @@
         <v>1498872</v>
       </c>
       <c r="C20" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D20" t="n">
         <v>30.57999534606934</v>
       </c>
     </row>
@@ -662,6 +724,9 @@
         <v>1157540</v>
       </c>
       <c r="C21" t="n">
+        <v>2.454331824</v>
+      </c>
+      <c r="D21" t="n">
         <v>30.617431640625</v>
       </c>
     </row>
@@ -673,6 +738,9 @@
         <v>1498872</v>
       </c>
       <c r="C22" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D22" t="n">
         <v>30.76394500732422</v>
       </c>
     </row>
@@ -684,6 +752,9 @@
         <v>1498872</v>
       </c>
       <c r="C23" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D23" t="n">
         <v>30.79811973571777</v>
       </c>
     </row>
@@ -695,6 +766,9 @@
         <v>1498872</v>
       </c>
       <c r="C24" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D24" t="n">
         <v>30.42163581848144</v>
       </c>
     </row>
@@ -706,6 +780,9 @@
         <v>1317974</v>
       </c>
       <c r="C25" t="n">
+        <v>2.8009827</v>
+      </c>
+      <c r="D25" t="n">
         <v>30.66983108520508</v>
       </c>
     </row>
@@ -717,6 +794,9 @@
         <v>1498872</v>
       </c>
       <c r="C26" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D26" t="n">
         <v>30.66650581359863</v>
       </c>
     </row>
@@ -728,6 +808,9 @@
         <v>1498872</v>
       </c>
       <c r="C27" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D27" t="n">
         <v>30.72971038818359</v>
       </c>
     </row>
@@ -739,6 +822,9 @@
         <v>1498872</v>
       </c>
       <c r="C28" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D28" t="n">
         <v>30.61976699829102</v>
       </c>
     </row>
@@ -750,6 +836,9 @@
         <v>1498872</v>
       </c>
       <c r="C29" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="D29" t="n">
         <v>30.81734657287598</v>
       </c>
     </row>
@@ -761,6 +850,9 @@
         <v>1317974</v>
       </c>
       <c r="C30" t="n">
+        <v>2.8009827</v>
+      </c>
+      <c r="D30" t="n">
         <v>30.72907943725586</v>
       </c>
     </row>
@@ -772,6 +864,9 @@
         <v>1154868</v>
       </c>
       <c r="C31" t="n">
+        <v>2.652512688</v>
+      </c>
+      <c r="D31" t="n">
         <v>30.89419708251953</v>
       </c>
     </row>
@@ -783,6 +878,9 @@
         <v>1496200</v>
       </c>
       <c r="C32" t="n">
+        <v>3.39697152</v>
+      </c>
+      <c r="D32" t="n">
         <v>30.93160247802734</v>
       </c>
     </row>
@@ -794,6 +892,9 @@
         <v>1320006</v>
       </c>
       <c r="C33" t="n">
+        <v>3.01331934</v>
+      </c>
+      <c r="D33" t="n">
         <v>30.86603202819824</v>
       </c>
     </row>
